--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrPlanAssetR.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrPlanAssetR.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ideaWorkSpace\2.1.0\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,6 +91,10 @@
   </si>
   <si>
     <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="11.125" customWidth="1"/>
@@ -479,7 +483,7 @@
     <col min="15" max="15" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -531,8 +535,11 @@
       <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
